--- a/vendor-performance/datasets/vendor-master.xlsx
+++ b/vendor-performance/datasets/vendor-master.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e29a6debf5eaf8e/Documents/GitHub/northstar-health-operations/vendor-performance/datasets/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_F25DC773A252ABDACC104871895B64DE5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{698764A3-7B5D-45E7-AC92-8E0F3AC0CE64}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="2685" yWindow="2685" windowWidth="23475" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,220 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="69">
+  <si>
+    <t>vendor_id</t>
+  </si>
+  <si>
+    <t>vendor_name</t>
+  </si>
+  <si>
+    <t>vendor_type</t>
+  </si>
+  <si>
+    <t>primary_service_category</t>
+  </si>
+  <si>
+    <t>support_level</t>
+  </si>
+  <si>
+    <t>risk_tier</t>
+  </si>
+  <si>
+    <t>preferred_vendor_flag</t>
+  </si>
+  <si>
+    <t>emergency_fulfillment_flag</t>
+  </si>
+  <si>
+    <t>active_vendor_flag</t>
+  </si>
+  <si>
+    <t>primary_contact_team</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>VEND-001</t>
+  </si>
+  <si>
+    <t>MedSupply Partners</t>
+  </si>
+  <si>
+    <t>Primary Supplier</t>
+  </si>
+  <si>
+    <t>Medical Supplies</t>
+  </si>
+  <si>
+    <t>Core Operational Support</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Supply &amp; Inventory Operations</t>
+  </si>
+  <si>
+    <t>Preferred supplier for routine medical supply replenishment.</t>
+  </si>
+  <si>
+    <t>VEND-002</t>
+  </si>
+  <si>
+    <t>TriPoint Clinical Logistics</t>
+  </si>
+  <si>
+    <t>Logistics Partner</t>
+  </si>
+  <si>
+    <t>Distribution Support</t>
+  </si>
+  <si>
+    <t>Logistics Support</t>
+  </si>
+  <si>
+    <t>Moderate</t>
+  </si>
+  <si>
+    <t>Supports regional shipment movement and distribution coordination.</t>
+  </si>
+  <si>
+    <t>VEND-003</t>
+  </si>
+  <si>
+    <t>Carolina Emergency Supply</t>
+  </si>
+  <si>
+    <t>Emergency Supplier</t>
+  </si>
+  <si>
+    <t>Emergency Supplies</t>
+  </si>
+  <si>
+    <t>Emergency Support</t>
+  </si>
+  <si>
+    <t>Operations Coordination Center</t>
+  </si>
+  <si>
+    <t>Used for urgent replenishment when critical supply continuity is at risk.</t>
+  </si>
+  <si>
+    <t>VEND-004</t>
+  </si>
+  <si>
+    <t>Northline Medical Equipment</t>
+  </si>
+  <si>
+    <t>Specialty Supplier</t>
+  </si>
+  <si>
+    <t>Clinical Equipment</t>
+  </si>
+  <si>
+    <t>Specialty Support</t>
+  </si>
+  <si>
+    <t>Provides specialty equipment with longer lead times.</t>
+  </si>
+  <si>
+    <t>VEND-005</t>
+  </si>
+  <si>
+    <t>Blue Ridge Fulfillment Group</t>
+  </si>
+  <si>
+    <t>Backup Supplier</t>
+  </si>
+  <si>
+    <t>Supplemental Support</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Vendor &amp; Service Management</t>
+  </si>
+  <si>
+    <t>Backup supplier with inconsistent fulfillment timing.</t>
+  </si>
+  <si>
+    <t>VEND-006</t>
+  </si>
+  <si>
+    <t>Oakwell Distribution Services</t>
+  </si>
+  <si>
+    <t>Recurring delivery delays require elevated monitoring.</t>
+  </si>
+  <si>
+    <t>VEND-007</t>
+  </si>
+  <si>
+    <t>Apex Procedural Supply</t>
+  </si>
+  <si>
+    <t>Primary supplier for procedure-related inventory items.</t>
+  </si>
+  <si>
+    <t>VEND-008</t>
+  </si>
+  <si>
+    <t>RapidCare Response Supply</t>
+  </si>
+  <si>
+    <t>Supports emergency fulfillment during shortage escalation events.</t>
+  </si>
+  <si>
+    <t>VEND-009</t>
+  </si>
+  <si>
+    <t>Precision Diagnostics Supply</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>High-dependency specialty vendor with operational risk exposure.</t>
+  </si>
+  <si>
+    <t>VEND-010</t>
+  </si>
+  <si>
+    <t>Evergreen General Operations</t>
+  </si>
+  <si>
+    <t>General Operations</t>
+  </si>
+  <si>
+    <t>Stable vendor for general operational supply needs.</t>
+  </si>
+  <si>
+    <t>VEND-011</t>
+  </si>
+  <si>
+    <t>Piedmont Medline Services</t>
+  </si>
+  <si>
+    <t>Supplemental vendor used when primary supply channels are constrained.</t>
+  </si>
+  <si>
+    <t>VEND-012</t>
+  </si>
+  <si>
+    <t>Legacy Regional Supplies</t>
+  </si>
+  <si>
+    <t>Inactive vendor retained for historical reporting continuity.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -330,10 +548,466 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s">
+        <v>44</v>
+      </c>
+      <c r="K10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="s">
+        <v>44</v>
+      </c>
+      <c r="K13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>